--- a/conference_registration_forms/016_global_conversation_registration--conference_registration_forms.xlsx
+++ b/conference_registration_forms/016_global_conversation_registration--conference_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'est'}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'EST'}</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'est_(est)'}</t>
+          <t>est_(est)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'EST (EST)'}</t>
+          <t>EST (EST)</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'cst'}</t>
+          <t>cst</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'CST'}</t>
+          <t>CST</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'mst'}</t>
+          <t>mst</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'MST'}</t>
+          <t>MST</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'pst'}</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'PST'}</t>
+          <t>PST</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'English', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'mandarin',_'label':_'mandarin'}</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Mandarin', 'label': 'Mandarin'}</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish', 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'french',_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'French', 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'language_exchange_group',_'label':_'language_exchange_group'}</t>
+          <t>language_exchange_group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Language Exchange Group', 'label': 'Language Exchange Group'}</t>
+          <t>Language Exchange Group</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'school/university',_'label':_'school/university'}</t>
+          <t>school/university</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'School/University', 'label': 'School/University'}</t>
+          <t>School/University</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
